--- a/app/MAU RP XUAT BAO CAO/KET QUA TN.xlsx
+++ b/app/MAU RP XUAT BAO CAO/KET QUA TN.xlsx
@@ -8,17 +8,26 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\web-giao-vucd\app\MAU RP XUAT BAO CAO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3F284C4-D857-491D-AEA5-FCEF61C2C3FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AAD5C2C-8305-42AA-8BC5-3DBFAEAD77AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
@@ -28,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="9">
   <si>
     <t>ma_dk</t>
   </si>
@@ -48,16 +57,13 @@
     <t>duong</t>
   </si>
   <si>
-    <t>77008-20260128-092912</t>
-  </si>
-  <si>
-    <t>77008-20260127-161459</t>
-  </si>
-  <si>
     <t>đạt</t>
   </si>
   <si>
-    <t>77008-20260127-161636</t>
+    <t>77008-20200624-181211</t>
+  </si>
+  <si>
+    <t>77008-20200624-181324</t>
   </si>
 </sst>
 </file>
@@ -376,7 +382,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="28.125" customWidth="1"/>
@@ -406,62 +412,42 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" s="1">
-        <v>46109</v>
+        <v>44137</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3" s="1">
-        <v>46109</v>
+        <v>44140</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="1">
-        <v>46109</v>
-      </c>
-      <c r="C4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/app/MAU RP XUAT BAO CAO/KET QUA TN.xlsx
+++ b/app/MAU RP XUAT BAO CAO/KET QUA TN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\web-giao-vucd\app\MAU RP XUAT BAO CAO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AAD5C2C-8305-42AA-8BC5-3DBFAEAD77AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D71DEB6-C82D-4AD3-8805-653415EF0B7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="8">
   <si>
     <t>ma_dk</t>
   </si>
@@ -60,10 +60,7 @@
     <t>đạt</t>
   </si>
   <si>
-    <t>77008-20200624-181211</t>
-  </si>
-  <si>
-    <t>77008-20200624-181324</t>
+    <t>77008-20200624-183717</t>
   </si>
 </sst>
 </file>
@@ -106,7 +103,18 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -382,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="28.125" customWidth="1"/>
@@ -415,7 +423,7 @@
         <v>7</v>
       </c>
       <c r="B2" s="1">
-        <v>44137</v>
+        <v>44140</v>
       </c>
       <c r="C2" t="s">
         <v>6</v>
@@ -430,27 +438,10 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="1">
-        <v>44140</v>
-      </c>
-      <c r="C3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" t="s">
-        <v>6</v>
-      </c>
-    </row>
   </sheetData>
+  <conditionalFormatting sqref="A2">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
